--- a/docs/matriz_rastreabilidade.xlsx
+++ b/docs/matriz_rastreabilidade.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +86,19 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -174,6 +185,26 @@
         <fgColor rgb="00E8D5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E86C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -245,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,6 +382,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6034,6 +6080,14 @@
           <t>▶  SPRINT 3 — HerbService, HerbRepository, PlanService, PlanRepository</t>
         </is>
       </c>
+      <c r="B122" s="37" t="n"/>
+      <c r="C122" s="37" t="n"/>
+      <c r="D122" s="37" t="n"/>
+      <c r="E122" s="37" t="n"/>
+      <c r="F122" s="37" t="n"/>
+      <c r="G122" s="37" t="n"/>
+      <c r="H122" s="37" t="n"/>
+      <c r="I122" s="38" t="n"/>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="40" t="inlineStr">
@@ -8150,15 +8204,4748 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t>▶  SPRINT 3 — Alerts — Classificador (classify_alert)</t>
+        </is>
+      </c>
+      <c r="B168" s="37" t="n"/>
+      <c r="C168" s="37" t="n"/>
+      <c r="D168" s="37" t="n"/>
+      <c r="E168" s="37" t="n"/>
+      <c r="F168" s="37" t="n"/>
+      <c r="G168" s="37" t="n"/>
+      <c r="H168" s="37" t="n"/>
+      <c r="I168" s="38" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-01</t>
+        </is>
+      </c>
+      <c r="B169" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C169" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D169" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E169" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F169" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1: temp e humidity dentro dos limites → None</t>
+        </is>
+      </c>
+      <c r="G169" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H169" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I169" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-02</t>
+        </is>
+      </c>
+      <c r="B170" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C170" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D170" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E170" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F170" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1: temp no limite inferior → None</t>
+        </is>
+      </c>
+      <c r="G170" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H170" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I170" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-03</t>
+        </is>
+      </c>
+      <c r="B171" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C171" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D171" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E171" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F171" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1: temp no limite superior → None</t>
+        </is>
+      </c>
+      <c r="G171" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H171" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I171" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-04</t>
+        </is>
+      </c>
+      <c r="B172" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C172" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D172" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E172" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F172" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1: humidity no limite inferior → None</t>
+        </is>
+      </c>
+      <c r="G172" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H172" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I172" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-05</t>
+        </is>
+      </c>
+      <c r="B173" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C173" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D173" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E173" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F173" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1: humidity no limite superior → None</t>
+        </is>
+      </c>
+      <c r="G173" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H173" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I173" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-06</t>
+        </is>
+      </c>
+      <c r="B174" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C174" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D174" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E174" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F174" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V2: só temp abaixo do mínimo, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G174" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H174" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I174" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-07</t>
+        </is>
+      </c>
+      <c r="B175" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C175" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D175" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E175" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F175" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V2: só temp acima do máximo, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G175" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H175" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I175" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-08</t>
+        </is>
+      </c>
+      <c r="B176" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C176" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D176" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E176" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F176" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V3: só humidity abaixo do mínimo, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G176" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H176" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I176" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-09</t>
+        </is>
+      </c>
+      <c r="B177" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C177" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D177" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E177" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F177" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V3: só humidity acima do máximo, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G177" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H177" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I177" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-10</t>
+        </is>
+      </c>
+      <c r="B178" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C178" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D178" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E178" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F178" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V4: ambos fora (temp↓ hum↓), sensor OK → "Crítico"</t>
+        </is>
+      </c>
+      <c r="G178" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H178" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I178" s="44" t="inlineStr">
+        <is>
+          <t>"Crítico"</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-11</t>
+        </is>
+      </c>
+      <c r="B179" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C179" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D179" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E179" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F179" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V4: ambos fora (temp↑ hum↑), sensor OK → "Crítico"</t>
+        </is>
+      </c>
+      <c r="G179" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H179" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I179" s="44" t="inlineStr">
+        <is>
+          <t>"Crítico"</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-12</t>
+        </is>
+      </c>
+      <c r="B180" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C180" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D180" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-02: sensor com falha → Informativo</t>
+        </is>
+      </c>
+      <c r="E180" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F180" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V5: sensor_ok=False, temp fora → "Informativo"</t>
+        </is>
+      </c>
+      <c r="G180" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H180" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I180" s="44" t="inlineStr">
+        <is>
+          <t>"Informativo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-13</t>
+        </is>
+      </c>
+      <c r="B181" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C181" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D181" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-02: sensor com falha → Informativo</t>
+        </is>
+      </c>
+      <c r="E181" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F181" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V5: sensor_ok=False, humidity fora → "Informativo"</t>
+        </is>
+      </c>
+      <c r="G181" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H181" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I181" s="44" t="inlineStr">
+        <is>
+          <t>"Informativo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-14</t>
+        </is>
+      </c>
+      <c r="B182" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C182" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D182" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-02: sensor com falha → Informativo</t>
+        </is>
+      </c>
+      <c r="E182" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F182" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V5: sensor_ok=False, ambos fora → "Informativo"</t>
+        </is>
+      </c>
+      <c r="G182" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H182" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I182" s="44" t="inlineStr">
+        <is>
+          <t>"Informativo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-15</t>
+        </is>
+      </c>
+      <c r="B183" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C183" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D183" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: classificar medição ambiental</t>
+        </is>
+      </c>
+      <c r="E183" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F183" s="44" t="inlineStr">
+        <is>
+          <t>EC-CLASS-I1: measurement sem chaves → None</t>
+        </is>
+      </c>
+      <c r="G183" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H183" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I183" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-16</t>
+        </is>
+      </c>
+      <c r="B184" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C184" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D184" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E184" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F184" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=F,C3=T: sem violações → None</t>
+        </is>
+      </c>
+      <c r="G184" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H184" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I184" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-17</t>
+        </is>
+      </c>
+      <c r="B185" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C185" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D185" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E185" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F185" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=F,C3=T: C1 muda resultado → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G185" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H185" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I185" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-18</t>
+        </is>
+      </c>
+      <c r="B186" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C186" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D186" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E186" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F186" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=T,C3=T: C2 muda resultado → "Aviso"</t>
+        </is>
+      </c>
+      <c r="G186" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H186" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I186" s="44" t="inlineStr">
+        <is>
+          <t>"Aviso"</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-19</t>
+        </is>
+      </c>
+      <c r="B187" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C187" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D187" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E187" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F187" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=F,C3=F: C3 muda resultado → "Informativo"</t>
+        </is>
+      </c>
+      <c r="G187" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H187" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I187" s="44" t="inlineStr">
+        <is>
+          <t>"Informativo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-20</t>
+        </is>
+      </c>
+      <c r="B188" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C188" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D188" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E188" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F188" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=T,C3=T: ambos fora, sensor OK → "Crítico"</t>
+        </is>
+      </c>
+      <c r="G188" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H188" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I188" s="44" t="inlineStr">
+        <is>
+          <t>"Crítico"</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-21</t>
+        </is>
+      </c>
+      <c r="B189" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C189" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier</t>
+        </is>
+      </c>
+      <c r="D189" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01: (C1 OR C2) AND C3</t>
+        </is>
+      </c>
+      <c r="E189" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F189" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=T,C3=F: C3 muda resultado vs C2=T → "Informativo"</t>
+        </is>
+      </c>
+      <c r="G189" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H189" s="44" t="inlineStr">
+        <is>
+          <t>classify_alert()</t>
+        </is>
+      </c>
+      <c r="I189" s="44" t="inlineStr">
+        <is>
+          <t>"Informativo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="43" t="inlineStr">
+        <is>
+          <t>▶  SPRINT 3 — Alerts — Resolutor (resolve_alert)</t>
+        </is>
+      </c>
+      <c r="B190" s="37" t="n"/>
+      <c r="C190" s="37" t="n"/>
+      <c r="D190" s="37" t="n"/>
+      <c r="E190" s="37" t="n"/>
+      <c r="F190" s="37" t="n"/>
+      <c r="G190" s="37" t="n"/>
+      <c r="H190" s="37" t="n"/>
+      <c r="I190" s="38" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-01</t>
+        </is>
+      </c>
+      <c r="B191" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C191" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D191" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E191" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F191" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-V1: status "Resolvido" sem justificação → sucesso</t>
+        </is>
+      </c>
+      <c r="G191" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H191" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I191" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Resolvido</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-02</t>
+        </is>
+      </c>
+      <c r="B192" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C192" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D192" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E192" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F192" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-V1: status "Resolvido" justification=None → sucesso</t>
+        </is>
+      </c>
+      <c r="G192" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H192" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I192" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Resolvido</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-03</t>
+        </is>
+      </c>
+      <c r="B193" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C193" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D193" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E193" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F193" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-V2: "Resolvido" com justificação curta (aceite)</t>
+        </is>
+      </c>
+      <c r="G193" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H193" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I193" s="44" t="inlineStr">
+        <is>
+          <t>dict com justificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-04</t>
+        </is>
+      </c>
+      <c r="B194" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C194" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D194" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E194" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F194" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-V2: "Resolvido" com justificação 1000 chars (aceite)</t>
+        </is>
+      </c>
+      <c r="G194" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H194" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I194" s="44" t="inlineStr">
+        <is>
+          <t>dict com justificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-05</t>
+        </is>
+      </c>
+      <c r="B195" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C195" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D195" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: ignorar com justificação</t>
+        </is>
+      </c>
+      <c r="E195" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F195" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-V3: "Ignorado" justificação 50 chars (interior) → sucesso</t>
+        </is>
+      </c>
+      <c r="G195" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H195" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I195" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Ignorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-06</t>
+        </is>
+      </c>
+      <c r="B196" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C196" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D196" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E196" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F196" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I1: status "Pendente" → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G196" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H196" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I196" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-07</t>
+        </is>
+      </c>
+      <c r="B197" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C197" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D197" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E197" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F197" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I1: status "" → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G197" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H197" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I197" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-08</t>
+        </is>
+      </c>
+      <c r="B198" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C198" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D198" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03: resolver alerta</t>
+        </is>
+      </c>
+      <c r="E198" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F198" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I1: status "resolvido" (case) → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G198" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H198" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I198" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-09</t>
+        </is>
+      </c>
+      <c r="B199" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C199" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D199" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: ignorar com justificação</t>
+        </is>
+      </c>
+      <c r="E199" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F199" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I2: "Ignorado" sem justificação → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G199" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H199" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I199" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-10</t>
+        </is>
+      </c>
+      <c r="B200" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C200" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D200" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: ignorar com justificação</t>
+        </is>
+      </c>
+      <c r="E200" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F200" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I2: "Ignorado" justification=None → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G200" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H200" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I200" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-11</t>
+        </is>
+      </c>
+      <c r="B201" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C201" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D201" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: ignorar com justificação</t>
+        </is>
+      </c>
+      <c r="E201" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F201" s="44" t="inlineStr">
+        <is>
+          <t>EC-RESV-I2: "Ignorado" justification="" → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G201" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H201" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I201" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-12</t>
+        </is>
+      </c>
+      <c r="B202" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C202" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D202" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: justificação [10,500] chars</t>
+        </is>
+      </c>
+      <c r="E202" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F202" s="44" t="inlineStr">
+        <is>
+          <t>VL fronteira inferior: 9 chars → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G202" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H202" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I202" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-13</t>
+        </is>
+      </c>
+      <c r="B203" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C203" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D203" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: justificação [10,500] chars</t>
+        </is>
+      </c>
+      <c r="E203" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F203" s="44" t="inlineStr">
+        <is>
+          <t>VL fronteira inferior: 10 chars → sucesso (mínimo válido)</t>
+        </is>
+      </c>
+      <c r="G203" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H203" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I203" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Ignorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-14</t>
+        </is>
+      </c>
+      <c r="B204" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C204" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D204" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: justificação [10,500] chars</t>
+        </is>
+      </c>
+      <c r="E204" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F204" s="44" t="inlineStr">
+        <is>
+          <t>VL ponto interior: 250 chars → sucesso</t>
+        </is>
+      </c>
+      <c r="G204" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H204" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I204" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Ignorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-15</t>
+        </is>
+      </c>
+      <c r="B205" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C205" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D205" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: justificação [10,500] chars</t>
+        </is>
+      </c>
+      <c r="E205" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F205" s="44" t="inlineStr">
+        <is>
+          <t>VL fronteira superior: 500 chars → sucesso (máximo válido)</t>
+        </is>
+      </c>
+      <c r="G205" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H205" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I205" s="44" t="inlineStr">
+        <is>
+          <t>dict status=Ignorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="44" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-16</t>
+        </is>
+      </c>
+      <c r="B206" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C206" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver</t>
+        </is>
+      </c>
+      <c r="D206" s="44" t="inlineStr">
+        <is>
+          <t>RN-ALERT-04: justificação [10,500] chars</t>
+        </is>
+      </c>
+      <c r="E206" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F206" s="44" t="inlineStr">
+        <is>
+          <t>VL fronteira superior: 501 chars → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="G206" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H206" s="44" t="inlineStr">
+        <is>
+          <t>resolve_alert()</t>
+        </is>
+      </c>
+      <c r="I206" s="44" t="inlineStr">
+        <is>
+          <t>AlertValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="43" t="inlineStr">
+        <is>
+          <t>▶  SPRINT 3 — Batches — Calculadora (calculate_productivity)</t>
+        </is>
+      </c>
+      <c r="B207" s="37" t="n"/>
+      <c r="C207" s="37" t="n"/>
+      <c r="D207" s="37" t="n"/>
+      <c r="E207" s="37" t="n"/>
+      <c r="F207" s="37" t="n"/>
+      <c r="G207" s="37" t="n"/>
+      <c r="H207" s="37" t="n"/>
+      <c r="I207" s="38" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-01</t>
+        </is>
+      </c>
+      <c r="B208" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C208" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D208" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E208" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F208" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V1: colhido=planeado, sem perdas → yield=1.0, loss=0.0</t>
+        </is>
+      </c>
+      <c r="G208" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H208" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I208" s="44" t="inlineStr">
+        <is>
+          <t>yield_rate=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-02</t>
+        </is>
+      </c>
+      <c r="B209" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C209" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D209" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E209" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F209" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V1: productivity_score=1.0 quando yield=time_eff=1.0</t>
+        </is>
+      </c>
+      <c r="G209" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H209" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I209" s="44" t="inlineStr">
+        <is>
+          <t>productivity_score=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-03</t>
+        </is>
+      </c>
+      <c r="B210" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C210" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D210" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E210" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F210" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V1: concluído antes do prazo → time_efficiency &gt; 1</t>
+        </is>
+      </c>
+      <c r="G210" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H210" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I210" s="44" t="inlineStr">
+        <is>
+          <t>time_efficiency&gt;1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-04</t>
+        </is>
+      </c>
+      <c r="B211" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C211" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D211" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: registar perdas</t>
+        </is>
+      </c>
+      <c r="E211" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F211" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V2: losses=20 → loss_rate=0.2</t>
+        </is>
+      </c>
+      <c r="G211" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H211" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I211" s="44" t="inlineStr">
+        <is>
+          <t>loss_rate=0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-05</t>
+        </is>
+      </c>
+      <c r="B212" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C212" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D212" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: registar perdas</t>
+        </is>
+      </c>
+      <c r="E212" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F212" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V2: losses=30 → yield=0.7, loss=0.3</t>
+        </is>
+      </c>
+      <c r="G212" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H212" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I212" s="44" t="inlineStr">
+        <is>
+          <t>yield=0.7, loss=0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-06</t>
+        </is>
+      </c>
+      <c r="B213" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C213" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D213" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E213" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F213" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-V3: harvested&lt;planned, losses=0 → yield_rate &lt; 1.0</t>
+        </is>
+      </c>
+      <c r="G213" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H213" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I213" s="44" t="inlineStr">
+        <is>
+          <t>yield_rate=0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-07</t>
+        </is>
+      </c>
+      <c r="B214" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C214" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D214" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E214" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F214" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I1: planned_qty=0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G214" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H214" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I214" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-08</t>
+        </is>
+      </c>
+      <c r="B215" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C215" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D215" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E215" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F215" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I1: planned_qty=-10 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G215" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H215" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I215" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-09</t>
+        </is>
+      </c>
+      <c r="B216" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C216" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D216" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E216" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F216" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I2: actual_days=None → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G216" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H216" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I216" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-10</t>
+        </is>
+      </c>
+      <c r="B217" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C217" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D217" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E217" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F217" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I2: actual_days=0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G217" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H217" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I217" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-11</t>
+        </is>
+      </c>
+      <c r="B218" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C218" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D218" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: calcular produtividade</t>
+        </is>
+      </c>
+      <c r="E218" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F218" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I2: actual_days=-5 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G218" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H218" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I218" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-12</t>
+        </is>
+      </c>
+      <c r="B219" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C219" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D219" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: registar perdas</t>
+        </is>
+      </c>
+      <c r="E219" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F219" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I3: harvested_qty=-10 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G219" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H219" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I219" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-13</t>
+        </is>
+      </c>
+      <c r="B220" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C220" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D220" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: registar perdas</t>
+        </is>
+      </c>
+      <c r="E220" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F220" s="44" t="inlineStr">
+        <is>
+          <t>EC-CALC-I4: losses=-5 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G220" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H220" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I220" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-14</t>
+        </is>
+      </c>
+      <c r="B221" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C221" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D221" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: planned_qty &gt; 0</t>
+        </is>
+      </c>
+      <c r="E221" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F221" s="44" t="inlineStr">
+        <is>
+          <t>VL planned_qty: 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G221" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H221" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I221" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-15</t>
+        </is>
+      </c>
+      <c r="B222" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C222" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D222" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: planned_qty &gt; 0</t>
+        </is>
+      </c>
+      <c r="E222" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F222" s="44" t="inlineStr">
+        <is>
+          <t>VL planned_qty: 1 → sucesso (mínimo válido)</t>
+        </is>
+      </c>
+      <c r="G222" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H222" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I222" s="44" t="inlineStr">
+        <is>
+          <t>yield_rate calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-16</t>
+        </is>
+      </c>
+      <c r="B223" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C223" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D223" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: actual_days &gt; 0</t>
+        </is>
+      </c>
+      <c r="E223" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F223" s="44" t="inlineStr">
+        <is>
+          <t>VL actual_days: None → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G223" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H223" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I223" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-17</t>
+        </is>
+      </c>
+      <c r="B224" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C224" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D224" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: actual_days &gt; 0</t>
+        </is>
+      </c>
+      <c r="E224" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F224" s="44" t="inlineStr">
+        <is>
+          <t>VL actual_days: 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G224" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H224" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I224" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-18</t>
+        </is>
+      </c>
+      <c r="B225" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C225" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D225" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01: actual_days &gt; 0</t>
+        </is>
+      </c>
+      <c r="E225" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F225" s="44" t="inlineStr">
+        <is>
+          <t>VL actual_days: 1 → sucesso (mínimo válido)</t>
+        </is>
+      </c>
+      <c r="G225" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H225" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I225" s="44" t="inlineStr">
+        <is>
+          <t>time_efficiency calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-19</t>
+        </is>
+      </c>
+      <c r="B226" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C226" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D226" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: harvested_qty &gt;= 0</t>
+        </is>
+      </c>
+      <c r="E226" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F226" s="44" t="inlineStr">
+        <is>
+          <t>VL harvested_qty: -1 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G226" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H226" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I226" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-20</t>
+        </is>
+      </c>
+      <c r="B227" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C227" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D227" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: harvested_qty &gt;= 0</t>
+        </is>
+      </c>
+      <c r="E227" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F227" s="44" t="inlineStr">
+        <is>
+          <t>VL harvested_qty: 0 → sucesso (fronteira válida)</t>
+        </is>
+      </c>
+      <c r="G227" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H227" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I227" s="44" t="inlineStr">
+        <is>
+          <t>yield_rate=0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-21</t>
+        </is>
+      </c>
+      <c r="B228" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C228" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D228" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: losses &gt;= 0</t>
+        </is>
+      </c>
+      <c r="E228" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F228" s="44" t="inlineStr">
+        <is>
+          <t>VL losses: -1 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G228" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H228" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I228" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-22</t>
+        </is>
+      </c>
+      <c r="B229" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C229" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator</t>
+        </is>
+      </c>
+      <c r="D229" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-02: losses &gt;= 0</t>
+        </is>
+      </c>
+      <c r="E229" s="44" t="inlineStr">
+        <is>
+          <t>VL</t>
+        </is>
+      </c>
+      <c r="F229" s="44" t="inlineStr">
+        <is>
+          <t>VL losses: 0 → sucesso (fronteira válida)</t>
+        </is>
+      </c>
+      <c r="G229" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H229" s="44" t="inlineStr">
+        <is>
+          <t>calculate_productivity()</t>
+        </is>
+      </c>
+      <c r="I229" s="44" t="inlineStr">
+        <is>
+          <t>loss_rate=0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="43" t="inlineStr">
+        <is>
+          <t>▶  SPRINT 3 — Batches — Máquina de Estados (transition_state)</t>
+        </is>
+      </c>
+      <c r="B230" s="37" t="n"/>
+      <c r="C230" s="37" t="n"/>
+      <c r="D230" s="37" t="n"/>
+      <c r="E230" s="37" t="n"/>
+      <c r="F230" s="37" t="n"/>
+      <c r="G230" s="37" t="n"/>
+      <c r="H230" s="37" t="n"/>
+      <c r="I230" s="38" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-01</t>
+        </is>
+      </c>
+      <c r="B231" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C231" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D231" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E231" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F231" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-V1: ativo → comprometido → sucesso</t>
+        </is>
+      </c>
+      <c r="G231" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H231" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I231" s="44" t="inlineStr">
+        <is>
+          <t>new_state=comprometido</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-02</t>
+        </is>
+      </c>
+      <c r="B232" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C232" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D232" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E232" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F232" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-V1: ativo → comprometido sem end_date → sucesso</t>
+        </is>
+      </c>
+      <c r="G232" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H232" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I232" s="44" t="inlineStr">
+        <is>
+          <t>new_state=comprometido</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-03</t>
+        </is>
+      </c>
+      <c r="B233" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C233" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D233" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E233" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F233" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-V2: ativo → concluído com end_date → sucesso</t>
+        </is>
+      </c>
+      <c r="G233" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H233" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I233" s="44" t="inlineStr">
+        <is>
+          <t>new_state=concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-04</t>
+        </is>
+      </c>
+      <c r="B234" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C234" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D234" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E234" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F234" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-V2: retorna dict com previous_state e new_state</t>
+        </is>
+      </c>
+      <c r="G234" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H234" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I234" s="44" t="inlineStr">
+        <is>
+          <t>dict com estados</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-05</t>
+        </is>
+      </c>
+      <c r="B235" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C235" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D235" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E235" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F235" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-V3: comprometido → ativo (reativação) → sucesso</t>
+        </is>
+      </c>
+      <c r="G235" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H235" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I235" s="44" t="inlineStr">
+        <is>
+          <t>new_state=ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-06</t>
+        </is>
+      </c>
+      <c r="B236" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C236" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D236" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições proibidas</t>
+        </is>
+      </c>
+      <c r="E236" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F236" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I1: concluído → ativo → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G236" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H236" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I236" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-07</t>
+        </is>
+      </c>
+      <c r="B237" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C237" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D237" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições proibidas</t>
+        </is>
+      </c>
+      <c r="E237" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F237" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I1: concluído → comprometido → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G237" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H237" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I237" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-08</t>
+        </is>
+      </c>
+      <c r="B238" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C238" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D238" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições proibidas</t>
+        </is>
+      </c>
+      <c r="E238" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F238" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I1: comprometido → concluído → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G238" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H238" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I238" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-09</t>
+        </is>
+      </c>
+      <c r="B239" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C239" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D239" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições proibidas</t>
+        </is>
+      </c>
+      <c r="E239" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F239" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I1: ativo → ativo → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G239" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H239" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I239" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-10</t>
+        </is>
+      </c>
+      <c r="B240" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C240" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D240" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: concluir requer end_date</t>
+        </is>
+      </c>
+      <c r="E240" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F240" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I2: ativo → concluído sem end_date → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G240" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H240" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I240" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-11</t>
+        </is>
+      </c>
+      <c r="B241" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C241" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D241" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: concluir requer end_date</t>
+        </is>
+      </c>
+      <c r="E241" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F241" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I2: ativo → concluído end_date=None → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G241" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H241" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I241" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-12</t>
+        </is>
+      </c>
+      <c r="B242" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C242" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D242" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E242" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F242" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I3: current_state inválido "inativo" → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G242" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H242" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I242" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-13</t>
+        </is>
+      </c>
+      <c r="B243" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C243" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D243" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E243" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F243" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I3: current_state="" → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G243" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H243" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I243" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-14</t>
+        </is>
+      </c>
+      <c r="B244" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C244" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D244" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E244" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F244" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I4: new_state inválido "cancelado" → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G244" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H244" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I244" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-15</t>
+        </is>
+      </c>
+      <c r="B245" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C245" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D245" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado</t>
+        </is>
+      </c>
+      <c r="E245" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F245" s="44" t="inlineStr">
+        <is>
+          <t>EC-SM-I4: new_state="" → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G245" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H245" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I245" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-16</t>
+        </is>
+      </c>
+      <c r="B246" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C246" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D246" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: pode_concluir = C1 AND C2</t>
+        </is>
+      </c>
+      <c r="E246" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F246" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=F: new≠concluído, sem end_date → comprometido</t>
+        </is>
+      </c>
+      <c r="G246" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H246" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I246" s="44" t="inlineStr">
+        <is>
+          <t>new_state=comprometido</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-17</t>
+        </is>
+      </c>
+      <c r="B247" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C247" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D247" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: pode_concluir = C1 AND C2</t>
+        </is>
+      </c>
+      <c r="E247" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F247" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=T: pode_concluir=True → concluído</t>
+        </is>
+      </c>
+      <c r="G247" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H247" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I247" s="44" t="inlineStr">
+        <is>
+          <t>new_state=concluído</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-18</t>
+        </is>
+      </c>
+      <c r="B248" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C248" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D248" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: pode_concluir = C1 AND C2</t>
+        </is>
+      </c>
+      <c r="E248" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F248" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=F: C2 muda resultado → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="G248" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H248" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I248" s="44" t="inlineStr">
+        <is>
+          <t>BatchValidationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="44" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-19</t>
+        </is>
+      </c>
+      <c r="B249" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C249" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine</t>
+        </is>
+      </c>
+      <c r="D249" s="44" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: pode_concluir = C1 AND C2</t>
+        </is>
+      </c>
+      <c r="E249" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F249" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=T: C1 muda resultado → comprometido (aceite)</t>
+        </is>
+      </c>
+      <c r="G249" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H249" s="44" t="inlineStr">
+        <is>
+          <t>transition_state()</t>
+        </is>
+      </c>
+      <c r="I249" s="44" t="inlineStr">
+        <is>
+          <t>new_state=comprometido</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="43" t="inlineStr">
+        <is>
+          <t>▶  SPRINT 3 — Automation — Motor de Regras (decide_action)</t>
+        </is>
+      </c>
+      <c r="B250" s="37" t="n"/>
+      <c r="C250" s="37" t="n"/>
+      <c r="D250" s="37" t="n"/>
+      <c r="E250" s="37" t="n"/>
+      <c r="F250" s="37" t="n"/>
+      <c r="G250" s="37" t="n"/>
+      <c r="H250" s="37" t="n"/>
+      <c r="I250" s="38" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-01</t>
+        </is>
+      </c>
+      <c r="B251" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C251" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D251" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo Automático → executar</t>
+        </is>
+      </c>
+      <c r="E251" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F251" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V1: Automático + regra ativa + dispara → "executar"</t>
+        </is>
+      </c>
+      <c r="G251" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H251" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I251" s="44" t="inlineStr">
+        <is>
+          <t>"executar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-02</t>
+        </is>
+      </c>
+      <c r="B252" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C252" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D252" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo Automático → executar</t>
+        </is>
+      </c>
+      <c r="E252" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F252" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V1: decide_action("Automático",T,T) == "executar"</t>
+        </is>
+      </c>
+      <c r="G252" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H252" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I252" s="44" t="inlineStr">
+        <is>
+          <t>"executar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-03</t>
+        </is>
+      </c>
+      <c r="B253" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C253" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D253" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-02: modo Manual → sugerir</t>
+        </is>
+      </c>
+      <c r="E253" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F253" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V2: Manual + regra ativa + dispara → "sugerir"</t>
+        </is>
+      </c>
+      <c r="G253" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H253" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I253" s="44" t="inlineStr">
+        <is>
+          <t>"sugerir"</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-04</t>
+        </is>
+      </c>
+      <c r="B254" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C254" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D254" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-02: modo Manual → sugerir</t>
+        </is>
+      </c>
+      <c r="E254" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F254" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V2: decide_action("Manual",T,T) == "sugerir"</t>
+        </is>
+      </c>
+      <c r="G254" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H254" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I254" s="44" t="inlineStr">
+        <is>
+          <t>"sugerir"</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-05</t>
+        </is>
+      </c>
+      <c r="B255" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C255" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D255" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-03: regra inativa → None</t>
+        </is>
+      </c>
+      <c r="E255" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F255" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V3: Automático + rule_active=False → None</t>
+        </is>
+      </c>
+      <c r="G255" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H255" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I255" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-06</t>
+        </is>
+      </c>
+      <c r="B256" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C256" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D256" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-03: regra inativa → None</t>
+        </is>
+      </c>
+      <c r="E256" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F256" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V3: Manual + rule_active=False → None</t>
+        </is>
+      </c>
+      <c r="G256" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H256" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I256" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-07</t>
+        </is>
+      </c>
+      <c r="B257" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C257" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D257" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-04: medição não dispara → None</t>
+        </is>
+      </c>
+      <c r="E257" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F257" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V4: Automático + triggers=False → None</t>
+        </is>
+      </c>
+      <c r="G257" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H257" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I257" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-08</t>
+        </is>
+      </c>
+      <c r="B258" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C258" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D258" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-04: medição não dispara → None</t>
+        </is>
+      </c>
+      <c r="E258" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F258" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V4: Manual + triggers=False → None</t>
+        </is>
+      </c>
+      <c r="G258" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H258" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I258" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-09</t>
+        </is>
+      </c>
+      <c r="B259" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C259" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D259" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-04: medição não dispara → None</t>
+        </is>
+      </c>
+      <c r="E259" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F259" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-V4: rule_active=F + triggers=False → None</t>
+        </is>
+      </c>
+      <c r="G259" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H259" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I259" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-10</t>
+        </is>
+      </c>
+      <c r="B260" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C260" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D260" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo inválido → erro</t>
+        </is>
+      </c>
+      <c r="E260" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F260" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-I1: mode="Semiautomático" → AutomationError</t>
+        </is>
+      </c>
+      <c r="G260" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H260" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I260" s="44" t="inlineStr">
+        <is>
+          <t>AutomationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-11</t>
+        </is>
+      </c>
+      <c r="B261" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C261" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D261" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo inválido → erro</t>
+        </is>
+      </c>
+      <c r="E261" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F261" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-I1: mode="" → AutomationError</t>
+        </is>
+      </c>
+      <c r="G261" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H261" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I261" s="44" t="inlineStr">
+        <is>
+          <t>AutomationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-12</t>
+        </is>
+      </c>
+      <c r="B262" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C262" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D262" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo inválido → erro</t>
+        </is>
+      </c>
+      <c r="E262" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F262" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-I1: mode="automático" (case) → AutomationError</t>
+        </is>
+      </c>
+      <c r="G262" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H262" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I262" s="44" t="inlineStr">
+        <is>
+          <t>AutomationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-13</t>
+        </is>
+      </c>
+      <c r="B263" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C263" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D263" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: modo inválido → erro</t>
+        </is>
+      </c>
+      <c r="E263" s="44" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="F263" s="44" t="inlineStr">
+        <is>
+          <t>EC-ENG-I1: mode=None → AutomationError/TypeError</t>
+        </is>
+      </c>
+      <c r="G263" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H263" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I263" s="44" t="inlineStr">
+        <is>
+          <t>AutomationError</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-14</t>
+        </is>
+      </c>
+      <c r="B264" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C264" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D264" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E264" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F264" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=T,C3=T: acionar=True → "executar" (caso base)</t>
+        </is>
+      </c>
+      <c r="G264" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H264" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I264" s="44" t="inlineStr">
+        <is>
+          <t>"executar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-15</t>
+        </is>
+      </c>
+      <c r="B265" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C265" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D265" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E265" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F265" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=T,C3=T: C1 muda resultado → "sugerir"</t>
+        </is>
+      </c>
+      <c r="G265" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H265" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I265" s="44" t="inlineStr">
+        <is>
+          <t>"sugerir"</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-16</t>
+        </is>
+      </c>
+      <c r="B266" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C266" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D266" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E266" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F266" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=F,C3=T: C2 muda resultado → None</t>
+        </is>
+      </c>
+      <c r="G266" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H266" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I266" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-17</t>
+        </is>
+      </c>
+      <c r="B267" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C267" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D267" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E267" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F267" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=T,C3=F: C3 muda resultado → None</t>
+        </is>
+      </c>
+      <c r="G267" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H267" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I267" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-18</t>
+        </is>
+      </c>
+      <c r="B268" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C268" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D268" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E268" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F268" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=F,C3=T → None</t>
+        </is>
+      </c>
+      <c r="G268" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H268" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I268" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-19</t>
+        </is>
+      </c>
+      <c r="B269" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C269" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D269" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E269" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F269" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=T,C3=F → None</t>
+        </is>
+      </c>
+      <c r="G269" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H269" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I269" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-20</t>
+        </is>
+      </c>
+      <c r="B270" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C270" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D270" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E270" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F270" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=T,C2=F,C3=F → None</t>
+        </is>
+      </c>
+      <c r="G270" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H270" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I270" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="44" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-21</t>
+        </is>
+      </c>
+      <c r="B271" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C271" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine</t>
+        </is>
+      </c>
+      <c r="D271" s="44" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01: acionar = C1 AND C2 AND C3</t>
+        </is>
+      </c>
+      <c r="E271" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC</t>
+        </is>
+      </c>
+      <c r="F271" s="44" t="inlineStr">
+        <is>
+          <t>MC/DC C1=F,C2=F,C3=F → None (todas False)</t>
+        </is>
+      </c>
+      <c r="G271" s="44" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
+      <c r="H271" s="44" t="inlineStr">
+        <is>
+          <t>decide_action()</t>
+        </is>
+      </c>
+      <c r="I271" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A63:I63"/>
     <mergeCell ref="A121:I121"/>
+    <mergeCell ref="A190:I190"/>
     <mergeCell ref="A117:I117"/>
+    <mergeCell ref="A230:I230"/>
+    <mergeCell ref="A207:I207"/>
+    <mergeCell ref="A250:I250"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A118:I118"/>
     <mergeCell ref="A120:I120"/>
+    <mergeCell ref="A168:I168"/>
     <mergeCell ref="A119:I119"/>
     <mergeCell ref="A122:I122"/>
     <mergeCell ref="A4:I4"/>
@@ -8173,7 +12960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9469,6 +14256,966 @@
       <c r="F42" s="18" t="inlineStr">
         <is>
           <t>TU-PLAN-PE-07, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="45" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B43" s="45" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V1</t>
+        </is>
+      </c>
+      <c r="C43" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D43" s="45" t="inlineStr">
+        <is>
+          <t>Todos os parâmetros dentro dos limites → None</t>
+        </is>
+      </c>
+      <c r="E43" s="45" t="inlineStr">
+        <is>
+          <t>temp=22, hum=60 (dentro)</t>
+        </is>
+      </c>
+      <c r="F43" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-01..05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="46" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V2</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>Só temperatura fora, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>temp=5 ou temp=35</t>
+        </is>
+      </c>
+      <c r="F44" s="46" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-06..07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="47" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V3</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D45" s="47" t="inlineStr">
+        <is>
+          <t>Só humidade fora, sensor OK → "Aviso"</t>
+        </is>
+      </c>
+      <c r="E45" s="47" t="inlineStr">
+        <is>
+          <t>hum=10 ou hum=95</t>
+        </is>
+      </c>
+      <c r="F45" s="47" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-08..09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V4</t>
+        </is>
+      </c>
+      <c r="C46" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D46" s="45" t="inlineStr">
+        <is>
+          <t>Ambos os parâmetros fora, sensor OK → "Crítico"</t>
+        </is>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>temp=5, hum=10</t>
+        </is>
+      </c>
+      <c r="F46" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-10..11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="46" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>EC-CLASS-V5</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="inlineStr">
+        <is>
+          <t>Sensor com falha, pelo menos um fora → "Informativo"</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="inlineStr">
+        <is>
+          <t>sensor_ok=False + violação</t>
+        </is>
+      </c>
+      <c r="F47" s="46" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-12..14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="47" t="inlineStr">
+        <is>
+          <t>Alerts — classify_alert</t>
+        </is>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>EC-CLASS-I1</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>Measurement sem chaves → None (sem dados)</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F48" s="47" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>Alerts — resolve_alert</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>EC-RESV-V1</t>
+        </is>
+      </c>
+      <c r="C49" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D49" s="45" t="inlineStr">
+        <is>
+          <t>"Resolvido" sem justificação → sucesso</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="inlineStr">
+        <is>
+          <t>status="Resolvido"</t>
+        </is>
+      </c>
+      <c r="F49" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-01..02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="46" t="inlineStr">
+        <is>
+          <t>Alerts — resolve_alert</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="inlineStr">
+        <is>
+          <t>EC-RESV-V2</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>"Resolvido" com justificação (qualquer comprimento) → aceite</t>
+        </is>
+      </c>
+      <c r="E50" s="46" t="inlineStr">
+        <is>
+          <t>justification="OK"</t>
+        </is>
+      </c>
+      <c r="F50" s="46" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-03..04</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="47" t="inlineStr">
+        <is>
+          <t>Alerts — resolve_alert</t>
+        </is>
+      </c>
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>EC-RESV-V3</t>
+        </is>
+      </c>
+      <c r="C51" s="47" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="inlineStr">
+        <is>
+          <t>"Ignorado" com justificação dentro de [10,500] → sucesso</t>
+        </is>
+      </c>
+      <c r="E51" s="47" t="inlineStr">
+        <is>
+          <t>justification="x"*50</t>
+        </is>
+      </c>
+      <c r="F51" s="47" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>Alerts — resolve_alert</t>
+        </is>
+      </c>
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>EC-RESV-I1</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D52" s="45" t="inlineStr">
+        <is>
+          <t>Estado não reconhecido → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>"Pendente", "", "resolvido"</t>
+        </is>
+      </c>
+      <c r="F52" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-06..08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="46" t="inlineStr">
+        <is>
+          <t>Alerts — resolve_alert</t>
+        </is>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>EC-RESV-I2</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>"Ignorado" sem justificação → AlertValidationError</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>justification=None, ""</t>
+        </is>
+      </c>
+      <c r="F53" s="46" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-09..11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="47" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B54" s="47" t="inlineStr">
+        <is>
+          <t>EC-CALC-V1</t>
+        </is>
+      </c>
+      <c r="C54" s="47" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D54" s="47" t="inlineStr">
+        <is>
+          <t>Lote sem perdas, colhido=planeado → yield=1.0, loss=0.0</t>
+        </is>
+      </c>
+      <c r="E54" s="47" t="inlineStr">
+        <is>
+          <t>planned=100, harvested=100, loss=0</t>
+        </is>
+      </c>
+      <c r="F54" s="47" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-01..03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="45" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B55" s="45" t="inlineStr">
+        <is>
+          <t>EC-CALC-V2</t>
+        </is>
+      </c>
+      <c r="C55" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D55" s="45" t="inlineStr">
+        <is>
+          <t>Lote com perdas (losses&gt;0) → loss_rate &gt; 0</t>
+        </is>
+      </c>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>losses=20 de 100 planeados</t>
+        </is>
+      </c>
+      <c r="F55" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-04..05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="46" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>EC-CALC-V3</t>
+        </is>
+      </c>
+      <c r="C56" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D56" s="46" t="inlineStr">
+        <is>
+          <t>Lote sem perdas, colhido&lt;planeado → yield_rate &lt; 1</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>harvested=60 de 100</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B57" s="47" t="inlineStr">
+        <is>
+          <t>EC-CALC-I1</t>
+        </is>
+      </c>
+      <c r="C57" s="47" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D57" s="47" t="inlineStr">
+        <is>
+          <t>planned_qty &lt;= 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E57" s="47" t="inlineStr">
+        <is>
+          <t>planned=0, planned=-10</t>
+        </is>
+      </c>
+      <c r="F57" s="47" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-07..08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="45" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B58" s="45" t="inlineStr">
+        <is>
+          <t>EC-CALC-I2</t>
+        </is>
+      </c>
+      <c r="C58" s="45" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D58" s="45" t="inlineStr">
+        <is>
+          <t>actual_days None ou &lt;= 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E58" s="45" t="inlineStr">
+        <is>
+          <t>actual_days=None, 0, -5</t>
+        </is>
+      </c>
+      <c r="F58" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-09..11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="46" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>EC-CALC-I3</t>
+        </is>
+      </c>
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="inlineStr">
+        <is>
+          <t>harvested_qty &lt; 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>harvested=-10</t>
+        </is>
+      </c>
+      <c r="F59" s="46" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="47" t="inlineStr">
+        <is>
+          <t>Batches — calculate_productivity</t>
+        </is>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>EC-CALC-I4</t>
+        </is>
+      </c>
+      <c r="C60" s="47" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D60" s="47" t="inlineStr">
+        <is>
+          <t>losses &lt; 0 → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E60" s="47" t="inlineStr">
+        <is>
+          <t>losses=-5</t>
+        </is>
+      </c>
+      <c r="F60" s="47" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="45" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B61" s="45" t="inlineStr">
+        <is>
+          <t>EC-SM-V1</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>ativo → comprometido: sempre permitido</t>
+        </is>
+      </c>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>current=ativo, new=comprometido</t>
+        </is>
+      </c>
+      <c r="F61" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-01..02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="46" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>EC-SM-V2</t>
+        </is>
+      </c>
+      <c r="C62" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="inlineStr">
+        <is>
+          <t>ativo → concluído com end_date: permitido</t>
+        </is>
+      </c>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>current=ativo, new=concluído + data</t>
+        </is>
+      </c>
+      <c r="F62" s="46" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-03..04</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="47" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B63" s="47" t="inlineStr">
+        <is>
+          <t>EC-SM-V3</t>
+        </is>
+      </c>
+      <c r="C63" s="47" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D63" s="47" t="inlineStr">
+        <is>
+          <t>comprometido → ativo: reativação permitida</t>
+        </is>
+      </c>
+      <c r="E63" s="47" t="inlineStr">
+        <is>
+          <t>current=comprometido, new=ativo</t>
+        </is>
+      </c>
+      <c r="F63" s="47" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="45" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>EC-SM-I1</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D64" s="45" t="inlineStr">
+        <is>
+          <t>transição proibida pela máquina de estados</t>
+        </is>
+      </c>
+      <c r="E64" s="45" t="inlineStr">
+        <is>
+          <t>concluído→ativo, comp.→concluído</t>
+        </is>
+      </c>
+      <c r="F64" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-06..09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="46" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>EC-SM-I2</t>
+        </is>
+      </c>
+      <c r="C65" s="46" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="inlineStr">
+        <is>
+          <t>ativo → concluído sem end_date → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>end_date=None</t>
+        </is>
+      </c>
+      <c r="F65" s="46" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-10..11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B66" s="47" t="inlineStr">
+        <is>
+          <t>EC-SM-I3</t>
+        </is>
+      </c>
+      <c r="C66" s="47" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D66" s="47" t="inlineStr">
+        <is>
+          <t>current_state não reconhecido → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E66" s="47" t="inlineStr">
+        <is>
+          <t>"inativo", ""</t>
+        </is>
+      </c>
+      <c r="F66" s="47" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-12..13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="45" t="inlineStr">
+        <is>
+          <t>Batches — transition_state</t>
+        </is>
+      </c>
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>EC-SM-I4</t>
+        </is>
+      </c>
+      <c r="C67" s="45" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>new_state não reconhecido → BatchValidationError</t>
+        </is>
+      </c>
+      <c r="E67" s="45" t="inlineStr">
+        <is>
+          <t>"cancelado", ""</t>
+        </is>
+      </c>
+      <c r="F67" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-14..15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="46" t="inlineStr">
+        <is>
+          <t>Automation — decide_action</t>
+        </is>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>EC-ENG-V1</t>
+        </is>
+      </c>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="inlineStr">
+        <is>
+          <t>Automático + regra ativa + dispara → "executar"</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>mode="Automático", T, T</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-01..02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="47" t="inlineStr">
+        <is>
+          <t>Automation — decide_action</t>
+        </is>
+      </c>
+      <c r="B69" s="47" t="inlineStr">
+        <is>
+          <t>EC-ENG-V2</t>
+        </is>
+      </c>
+      <c r="C69" s="47" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D69" s="47" t="inlineStr">
+        <is>
+          <t>Manual + regra ativa + dispara → "sugerir"</t>
+        </is>
+      </c>
+      <c r="E69" s="47" t="inlineStr">
+        <is>
+          <t>mode="Manual", T, T</t>
+        </is>
+      </c>
+      <c r="F69" s="47" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-03..04</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="45" t="inlineStr">
+        <is>
+          <t>Automation — decide_action</t>
+        </is>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>EC-ENG-V3</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="inlineStr">
+        <is>
+          <t>Regra inativa (C2=False) → None</t>
+        </is>
+      </c>
+      <c r="E70" s="45" t="inlineStr">
+        <is>
+          <t>rule_active=False</t>
+        </is>
+      </c>
+      <c r="F70" s="45" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-05..06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="46" t="inlineStr">
+        <is>
+          <t>Automation — decide_action</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>EC-ENG-V4</t>
+        </is>
+      </c>
+      <c r="C71" s="46" t="inlineStr">
+        <is>
+          <t>Válida</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>Medição não dispara (C3=False) → None</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>measurement_triggers_rule=False</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-07..09</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="47" t="inlineStr">
+        <is>
+          <t>Automation — decide_action</t>
+        </is>
+      </c>
+      <c r="B72" s="47" t="inlineStr">
+        <is>
+          <t>EC-ENG-I1</t>
+        </is>
+      </c>
+      <c r="C72" s="47" t="inlineStr">
+        <is>
+          <t>Inválida</t>
+        </is>
+      </c>
+      <c r="D72" s="47" t="inlineStr">
+        <is>
+          <t>Modo inválido → AutomationError</t>
+        </is>
+      </c>
+      <c r="E72" s="47" t="inlineStr">
+        <is>
+          <t>"Semiautomático", "", None</t>
+        </is>
+      </c>
+      <c r="F72" s="47" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-10..13</t>
         </is>
       </c>
     </row>
@@ -9486,7 +15233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9613,66 +15360,166 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Classifier (TU-ALERT-CLASS)</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>PE, MC/DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>Alerts — Resolver (TU-ALERT-RESV)</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>PE, VL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Batches — Calculator (TU-BATCH-CALC)</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>PE, VL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Batches — State Machine (TU-BATCH-SM)</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>PE, MC/DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>Automation — Engine (TU-AUTO-ENG)</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>PE, MC/DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
-        <v>112</v>
-      </c>
-      <c r="D9" s="28" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="C14" s="29" t="n">
+        <v>211</v>
+      </c>
+      <c r="D14" s="28" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Casos de Teste por Técnica</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Técnica</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>N.º de Casos</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>Particionamento de Equivalência (PE)</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="B19" s="31" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Análise de Valores Limite (VL)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="B20" s="33" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Cobertura MC/DC</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>9</v>
+      <c r="B21" s="35" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -9691,7 +15538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9979,6 +15826,91 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>RN-ALERT-01/02: classificar medição ambiental / sensor com falha</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-CLASS-01..15 (PE) | TU-ALERT-CLASS-16..21 (MC/DC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>RN-ALERT-03/04: resolver alerta / ignorar com justificação [10,500]</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>TU-ALERT-RESV-01..11 (PE) | TU-ALERT-RESV-12..16 (VL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>RN-BATCH-01/02: calcular produtividade / registar perdas</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-CALC-01..13 (PE) | TU-BATCH-CALC-14..22 (VL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>RN-BATCH-03: transições de estado do lote (máquina de estados)</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>TU-BATCH-SM-01..15 (PE) | TU-BATCH-SM-16..19 (MC/DC: C1 AND C2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>RN-AUTO-01..04: motor de automação (modo, regra, medição)</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C23" s="45" t="inlineStr">
+        <is>
+          <t>TU-AUTO-ENG-01..13 (PE) | TU-AUTO-ENG-14..21 (MC/DC: C1 AND C2 AND C3)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
